--- a/target_excel/WBS_公版原始設計.xlsx
+++ b/target_excel/WBS_公版原始設計.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t xml:space="preserve">WBS 編號</t>
   </si>
@@ -30,18 +30,18 @@
     <t>工作項目</t>
   </si>
   <si>
-    <t>交付物</t>
-  </si>
-  <si>
     <t>負責人</t>
   </si>
   <si>
-    <t>開始日</t>
+    <t>預計開始日</t>
   </si>
   <si>
     <t>預計結束日</t>
   </si>
   <si>
+    <t>實際開始日</t>
+  </si>
+  <si>
     <t>實際完成日</t>
   </si>
   <si>
@@ -51,9 +51,6 @@
     <t>狀態</t>
   </si>
   <si>
-    <t>風險等級</t>
-  </si>
-  <si>
     <t>備註</t>
   </si>
   <si>
@@ -63,13 +60,7 @@
     <t>待開始</t>
   </si>
   <si>
-    <t>高</t>
-  </si>
-  <si>
     <t>進行中</t>
-  </si>
-  <si>
-    <t>中</t>
   </si>
   <si>
     <t>風險</t>
@@ -168,7 +159,7 @@
   <cellStyleXfs count="1">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" quotePrefix="0" pivotButton="0"/>
     <xf fontId="1" fillId="2" borderId="1" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center" vertical="center"/>
@@ -186,9 +177,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf fontId="3" fillId="4" borderId="0" numFmtId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" quotePrefix="0" pivotButton="0">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyAlignment="1" quotePrefix="0" pivotButton="0">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -717,14 +705,16 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="14.57421875"/>
-    <col customWidth="1" min="2" max="2" width="10"/>
+    <col customWidth="1" min="2" max="2" width="22.28125"/>
     <col customWidth="1" min="3" max="3" width="24"/>
-    <col customWidth="1" min="4" max="4" width="14"/>
-    <col customWidth="1" min="5" max="5" width="8"/>
-    <col customWidth="1" min="6" max="8" width="12"/>
-    <col customWidth="1" min="9" max="10" width="8"/>
-    <col customWidth="1" min="11" max="11" width="11.140625"/>
-    <col customWidth="1" min="12" max="12" width="24"/>
+    <col customWidth="1" min="4" max="4" width="13.140625"/>
+    <col customWidth="1" min="5" max="5" width="20.140625"/>
+    <col customWidth="1" min="6" max="6" width="12"/>
+    <col customWidth="1" min="7" max="7" width="15.28125"/>
+    <col customWidth="1" min="8" max="8" width="12"/>
+    <col customWidth="1" min="9" max="9" width="11.421875"/>
+    <col customWidth="1" min="10" max="10" width="13.140625"/>
+    <col customWidth="1" min="11" max="11" width="24"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -760,9 +750,6 @@
       </c>
       <c r="K1" s="1" t="s">
         <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
       </c>
     </row>
     <row r="2" ht="18" customHeight="1">
@@ -779,7 +766,6 @@
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
       <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
     </row>
     <row r="3" ht="18" customHeight="1">
       <c r="A3" s="2"/>
@@ -795,7 +781,6 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2"/>
-      <c r="N3" s="2"/>
     </row>
     <row r="4" ht="18" customHeight="1">
       <c r="A4" s="2"/>
@@ -811,7 +796,6 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
-      <c r="N4" s="2"/>
     </row>
     <row r="5" ht="18" customHeight="1">
       <c r="A5" s="2"/>
@@ -827,7 +811,6 @@
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
-      <c r="N5" s="2"/>
     </row>
     <row r="6" ht="18" customHeight="1">
       <c r="A6" s="2"/>
@@ -843,7 +826,6 @@
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
-      <c r="N6" s="2"/>
     </row>
     <row r="7" ht="18" customHeight="1">
       <c r="A7" s="2"/>
@@ -859,7 +841,6 @@
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
-      <c r="N7" s="2"/>
     </row>
     <row r="8" ht="18" customHeight="1">
       <c r="A8" s="2"/>
@@ -875,7 +856,6 @@
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
-      <c r="N8" s="2"/>
     </row>
     <row r="9" ht="18" customHeight="1">
       <c r="A9" s="2"/>
@@ -891,7 +871,6 @@
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
-      <c r="N9" s="2"/>
     </row>
     <row r="10" ht="18" customHeight="1">
       <c r="A10" s="2"/>
@@ -907,7 +886,6 @@
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
-      <c r="N10" s="2"/>
     </row>
     <row r="11" ht="18" customHeight="1">
       <c r="A11" s="2"/>
@@ -923,7 +901,6 @@
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
     </row>
     <row r="12" ht="18" customHeight="1">
       <c r="A12" s="2"/>
@@ -939,7 +916,6 @@
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
-      <c r="N12" s="2"/>
     </row>
     <row r="13" ht="18" customHeight="1">
       <c r="A13" s="2"/>
@@ -955,7 +931,6 @@
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
-      <c r="N13" s="2"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="2"/>
@@ -971,7 +946,6 @@
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
-      <c r="N14" s="2"/>
     </row>
     <row r="15" ht="18" customHeight="1">
       <c r="A15" s="2"/>
@@ -987,7 +961,6 @@
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
-      <c r="N15" s="2"/>
     </row>
     <row r="16" ht="18" customHeight="1">
       <c r="A16" s="2"/>
@@ -1003,7 +976,6 @@
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
-      <c r="N16" s="2"/>
     </row>
     <row r="17" ht="18" customHeight="1">
       <c r="A17" s="2"/>
@@ -1019,7 +991,6 @@
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
-      <c r="N17" s="2"/>
     </row>
     <row r="18" ht="18" customHeight="1">
       <c r="A18" s="2"/>
@@ -1035,7 +1006,6 @@
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
-      <c r="N18" s="2"/>
     </row>
     <row r="19" ht="18" customHeight="1">
       <c r="A19" s="2"/>
@@ -1049,7 +1019,6 @@
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
-      <c r="L19" s="2"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="2"/>
@@ -1063,7 +1032,6 @@
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
-      <c r="L20" s="2"/>
     </row>
     <row r="21" ht="18" customHeight="1">
       <c r="A21" s="2"/>
@@ -1077,7 +1045,6 @@
       <c r="I21" s="2"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
-      <c r="L21" s="2"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0"/>
@@ -1097,10 +1064,10 @@
   <sheetData>
     <row r="1" ht="14.25">
       <c r="B1" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
@@ -1113,56 +1080,45 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac">
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.25"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="16.140625"/>
     <col customWidth="1" min="2" max="2" style="5" width="17.28125"/>
-    <col customWidth="1" min="3" max="3" style="5" width="17.00390625"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>10</v>
-      </c>
     </row>
     <row r="2">
       <c r="B2" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3">
       <c r="B3" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4">
       <c r="B4" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" s="5"/>
+        <v>14</v>
+      </c>
     </row>
     <row r="5">
       <c r="B5" s="5" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6">
-      <c r="B6" s="7" t="s">
-        <v>19</v>
+      <c r="B6" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
   </sheetData>
